--- a/Config/Datas/human_civilization.xlsx
+++ b/Config/Datas/human_civilization.xlsx
@@ -539,12 +539,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>??????????????</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -564,12 +564,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>初识文明</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>????????</t>
+          <t>开始理解人类聚落的基本运作。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -584,12 +584,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>聚落成形</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>????????????</t>
+          <t>已掌握若干基础技术，城镇功能开始成形。</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>?????</t>
+          <t>城镇协作</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>?????????????</t>
+          <t>多项技术形成协作网络，生产与探索开始互相支撑。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -624,12 +624,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>文明雏形</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>??????????????</t>
+          <t>人类城镇具备稳定的知识传承与生产体系。</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
